--- a/docs/talent_design.xlsx
+++ b/docs/talent_design.xlsx
@@ -1,50 +1,307 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongb0\Projects\dig_godot\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2976A31-649F-4672-AFFC-BDFEB1BC2316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5456CE26-4DEF-4F91-94B6-B7440472D588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Rule" sheetId="3" r:id="rId1"/>
+    <sheet name="Basic" sheetId="1" r:id="rId2"/>
+    <sheet name="Advanced" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="75">
+  <si>
+    <t>稿子方面加成-1</t>
+  </si>
+  <si>
+    <t>金币加成-100</t>
+  </si>
   <si>
     <t>重置所有 存储声望等加成 结算升华点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>稿子方面加成-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金币加成-100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矿石加成-5</t>
   </si>
   <si>
     <t>地块方面加成-10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>矿石加成-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命名规则：每个格子 = 天赋放置位置；内容 = 「天赋名-解锁金币」</t>
+  </si>
+  <si>
+    <t>分支方向：上=稿子 | 左=金币 | 右=矿石 | 下=地块</t>
+  </si>
+  <si>
+    <t>成本曲线：每向外一圈成本 ×1000 —— 第1圈(1~100) → 第2圈(1K~100K) → 第3圈(1M~100M) → 第4圈(1B~100B)</t>
+  </si>
+  <si>
+    <t>中心【重置】：重置所有金币与天赋，按历史最高累计金币结算升华点</t>
+  </si>
+  <si>
+    <t>升华点：每累计 100 万（及每升一个数量级）获得 1 升华点 +1% 永久金币倍率</t>
+  </si>
+  <si>
+    <t>两套天赋点：本表(Basic) = 金币解锁天赋；升华点天赋在「Advanced」表设计</t>
+  </si>
+  <si>
+    <t>升华天赋（Advanced）—— 用升华点购买</t>
+  </si>
+  <si>
+    <t>升华点获取：每累计 100 万金币（含更高数量级）获得 1 升华点 +1% 永久金币倍率</t>
+  </si>
+  <si>
+    <t>解锁草地-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁岩石-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁水-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁铁矿-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁金矿-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子基础伤害-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击几率-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击几率-500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害-10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子作用范围-1000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁火焰-1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁pull-10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁push-10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁spawn-100000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁火山-10000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁upgrade-100000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁rarity-1000000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁锌矿-100000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁绿宝石-1000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁钻石-100000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁黑曜石-100000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁水晶-10000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁煤炭-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁小猫矿-100000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子的收益提升1%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子的收益提升1%-200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子的收益提升1%-2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子的收益提升1%-20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级煤炭-200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大每台-2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地块的效率提升10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草地升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩石升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pull升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>push升级</t>
+  </si>
+  <si>
+    <t>spawn升级</t>
+  </si>
+  <si>
+    <t>火山升级</t>
+  </si>
+  <si>
+    <t>upgrade升级</t>
+  </si>
+  <si>
+    <t>rarity升级</t>
+  </si>
+  <si>
+    <t>高级铁矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级金矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级锌矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级绿宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级黑曜石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级水晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级小猫矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大铁矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大金矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大锌矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大绿宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大黑曜石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大水晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨大小猫矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稿子基础伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击几率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击几率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>稿子作用范围</t>
   </si>
 </sst>
 </file>
@@ -368,34 +625,502 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7641029-4561-48D8-9044-3DA9ED23C74D}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="F10:H12"/>
+  <dimension ref="C4:R23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="6" max="6" width="12.34765625" customWidth="1"/>
+    <col min="3" max="3" width="22.04296875" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="22.6484375" customWidth="1"/>
     <col min="7" max="7" width="39.34765625" customWidth="1"/>
-    <col min="8" max="8" width="14.953125" customWidth="1"/>
+    <col min="8" max="9" width="14.953125" customWidth="1"/>
+    <col min="10" max="11" width="14.04296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="6:8" x14ac:dyDescent="0.65">
-      <c r="G10" t="s">
+    <row r="4" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>60</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="6:8" x14ac:dyDescent="0.65">
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>2</v>
       </c>
-      <c r="G11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="6:8" x14ac:dyDescent="0.65">
-      <c r="G12" t="s">
-        <v>3</v>
+      <c r="L13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="3:18" x14ac:dyDescent="0.65">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" x14ac:dyDescent="0.65">
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <cols>
+    <col min="1" max="1" width="73.78125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.65">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/talent_design.xlsx
+++ b/docs/talent_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongb0\Projects\dig_godot\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5456CE26-4DEF-4F91-94B6-B7440472D588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B57E84-175A-4286-B1C8-D0C5B1EF7CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="3" r:id="rId1"/>
